--- a/Tab breakdown.xlsx
+++ b/Tab breakdown.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wadle\Desktop\CCAS\CCAS APP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F16ED29F-F1CB-4558-B4C6-9879ED375220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{544C8C8C-2E18-44C1-8596-CB0E02CE9247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D07FC0D3-806A-416F-96A7-8FFC247C9C43}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{D07FC0D3-806A-416F-96A7-8FFC247C9C43}"/>
   </bookViews>
   <sheets>
     <sheet name="Names" sheetId="1" r:id="rId1"/>
@@ -114,6 +114,9 @@
     <t>Shunt-dep SV for noncardiac Sx</t>
   </si>
   <si>
+    <t>Glenn for noncaridac Sx</t>
+  </si>
+  <si>
     <t>TEG</t>
   </si>
   <si>
@@ -340,9 +343,6 @@
   </si>
   <si>
     <t>summary (here include s/s)</t>
-  </si>
-  <si>
-    <t>Glenn for noncardiac Sx</t>
   </si>
 </sst>
 </file>
@@ -728,10 +728,10 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -744,19 +744,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -764,19 +764,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -784,19 +784,19 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -804,19 +804,19 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -824,19 +824,19 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -844,22 +844,22 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -867,22 +867,22 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -890,13 +890,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -904,16 +904,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -921,22 +921,22 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -944,13 +944,13 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -958,22 +958,22 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -981,22 +981,22 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -1004,19 +1004,19 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -1024,19 +1024,19 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -1044,22 +1044,22 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -1067,19 +1067,19 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -1087,16 +1087,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -1104,22 +1104,22 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -1127,22 +1127,22 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -1150,22 +1150,22 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -1173,22 +1173,22 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D23" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -1196,33 +1196,33 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -1230,13 +1230,13 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D26" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -1244,107 +1244,107 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>101</v>
+        <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C28" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E28" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" t="s">
         <v>65</v>
       </c>
-      <c r="C29" t="s">
-        <v>64</v>
-      </c>
       <c r="D29" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C30" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C31" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C32" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F32" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1367,183 +1367,183 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" t="s">
         <v>52</v>
       </c>
-      <c r="E1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F1" t="s">
-        <v>51</v>
-      </c>
       <c r="G1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1" t="s">
         <v>82</v>
-      </c>
-      <c r="H1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" t="s">
         <v>72</v>
-      </c>
-      <c r="E3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G3" t="s">
-        <v>84</v>
-      </c>
-      <c r="H3" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G4" t="s">
+        <v>86</v>
+      </c>
+      <c r="H4" t="s">
         <v>73</v>
-      </c>
-      <c r="E4" t="s">
-        <v>89</v>
-      </c>
-      <c r="F4" t="s">
-        <v>70</v>
-      </c>
-      <c r="G4" t="s">
-        <v>85</v>
-      </c>
-      <c r="H4" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E5" t="s">
         <v>43</v>
       </c>
-      <c r="B5" t="s">
+      <c r="F5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" t="s">
+        <v>87</v>
+      </c>
+      <c r="H5" t="s">
         <v>74</v>
-      </c>
-      <c r="C5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" t="s">
-        <v>86</v>
-      </c>
-      <c r="H5" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H6" t="s">
         <v>76</v>
-      </c>
-      <c r="E6" t="s">
-        <v>54</v>
-      </c>
-      <c r="F6" t="s">
-        <v>74</v>
-      </c>
-      <c r="G6" t="s">
-        <v>87</v>
-      </c>
-      <c r="H6" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/Tab breakdown.xlsx
+++ b/Tab breakdown.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wadle\Desktop\CCAS\CCAS APP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F16ED29F-F1CB-4558-B4C6-9879ED375220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2864DAF4-1E9E-4D39-8439-8D8565AC6572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D07FC0D3-806A-416F-96A7-8FFC247C9C43}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{D07FC0D3-806A-416F-96A7-8FFC247C9C43}"/>
   </bookViews>
   <sheets>
     <sheet name="Names" sheetId="1" r:id="rId1"/>
@@ -198,9 +198,6 @@
     <t>Code</t>
   </si>
   <si>
-    <t>Actions</t>
-  </si>
-  <si>
     <t>Other Considerations</t>
   </si>
   <si>
@@ -343,6 +340,9 @@
   </si>
   <si>
     <t>Glenn for noncardiac Sx</t>
+  </si>
+  <si>
+    <t>Quick Actions</t>
   </si>
 </sst>
 </file>
@@ -787,10 +787,10 @@
         <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s">
         <v>31</v>
@@ -810,7 +810,7 @@
         <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
         <v>31</v>
@@ -827,10 +827,10 @@
         <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
         <v>31</v>
@@ -850,7 +850,7 @@
         <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
         <v>31</v>
@@ -870,13 +870,13 @@
         <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
         <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F8" t="s">
         <v>32</v>
@@ -890,10 +890,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
         <v>29</v>
@@ -907,7 +907,7 @@
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
         <v>32</v>
@@ -927,7 +927,7 @@
         <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
         <v>31</v>
@@ -944,10 +944,10 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" t="s">
         <v>60</v>
-      </c>
-      <c r="C12" t="s">
-        <v>61</v>
       </c>
       <c r="D12" t="s">
         <v>29</v>
@@ -964,7 +964,7 @@
         <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
         <v>31</v>
@@ -987,7 +987,7 @@
         <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s">
         <v>31</v>
@@ -1004,10 +1004,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s">
         <v>31</v>
@@ -1027,10 +1027,10 @@
         <v>30</v>
       </c>
       <c r="C16" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" t="s">
         <v>62</v>
-      </c>
-      <c r="D16" t="s">
-        <v>63</v>
       </c>
       <c r="E16" t="s">
         <v>31</v>
@@ -1050,7 +1050,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E17" t="s">
         <v>31</v>
@@ -1070,7 +1070,7 @@
         <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D18" t="s">
         <v>31</v>
@@ -1090,7 +1090,7 @@
         <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
         <v>31</v>
@@ -1107,7 +1107,7 @@
         <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D20" t="s">
         <v>31</v>
@@ -1130,10 +1130,10 @@
         <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E21" t="s">
         <v>31</v>
@@ -1156,7 +1156,7 @@
         <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E22" t="s">
         <v>31</v>
@@ -1179,7 +1179,7 @@
         <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E23" t="s">
         <v>31</v>
@@ -1202,7 +1202,7 @@
         <v>33</v>
       </c>
       <c r="D24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E24" t="s">
         <v>31</v>
@@ -1222,7 +1222,7 @@
         <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -1230,10 +1230,10 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" t="s">
         <v>66</v>
-      </c>
-      <c r="C26" t="s">
-        <v>67</v>
       </c>
       <c r="D26" t="s">
         <v>29</v>
@@ -1258,13 +1258,13 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B28" t="s">
         <v>30</v>
       </c>
       <c r="C28" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D28" t="s">
         <v>35</v>
@@ -1281,10 +1281,10 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D29" t="s">
         <v>29</v>
@@ -1295,13 +1295,13 @@
         <v>26</v>
       </c>
       <c r="B30" t="s">
+        <v>98</v>
+      </c>
+      <c r="C30" t="s">
         <v>99</v>
       </c>
-      <c r="C30" t="s">
-        <v>100</v>
-      </c>
       <c r="D30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E30" t="s">
         <v>31</v>
@@ -1335,7 +1335,7 @@
         <v>33</v>
       </c>
       <c r="D32" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E32" t="s">
         <v>31</v>
@@ -1367,7 +1367,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B1" t="s">
         <v>51</v>
@@ -1376,16 +1376,16 @@
         <v>52</v>
       </c>
       <c r="E1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F1" t="s">
         <v>51</v>
       </c>
       <c r="G1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -1396,19 +1396,19 @@
         <v>45</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E2" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="F2" t="s">
         <v>46</v>
       </c>
       <c r="G2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -1416,10 +1416,10 @@
         <v>41</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
         <v>48</v>
@@ -1428,10 +1428,10 @@
         <v>45</v>
       </c>
       <c r="G3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -1442,19 +1442,19 @@
         <v>47</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -1462,10 +1462,10 @@
         <v>43</v>
       </c>
       <c r="B5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" t="s">
         <v>74</v>
-      </c>
-      <c r="C5" t="s">
-        <v>75</v>
       </c>
       <c r="E5" t="s">
         <v>42</v>
@@ -1474,10 +1474,10 @@
         <v>47</v>
       </c>
       <c r="G5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -1488,19 +1488,19 @@
         <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G6" t="s">
+        <v>86</v>
+      </c>
+      <c r="H6" t="s">
         <v>74</v>
-      </c>
-      <c r="G6" t="s">
-        <v>87</v>
-      </c>
-      <c r="H6" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -1511,7 +1511,7 @@
         <v>50</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
         <v>29</v>
@@ -1520,30 +1520,30 @@
         <v>50</v>
       </c>
       <c r="G7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
